--- a/example/99-Ponte completo GPC/REV004/Combinazioni_REV004.xlsx
+++ b/example/99-Ponte completo GPC/REV004/Combinazioni_REV004.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.00019893901674492397</t>
+          <t xml:space="preserve">-0.0003171439341670765</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
